--- a/public/exports-60-250/29189382.xlsx
+++ b/public/exports-60-250/29189382.xlsx
@@ -3866,7 +3866,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slettingenvej 51</t>
+          <t xml:space="preserve">Skagensvej 200A</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3876,40 +3876,40 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403342</t>
+          <t xml:space="preserve">9028182</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J52">
-        <v>85</v>
+        <v>153</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199559</t>
+          <t xml:space="preserve">311466005</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t xml:space="preserve">JPH Energi A/S</t>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slettingenvej 51</t>
+          <t xml:space="preserve">Idrætsmarken 15B</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3951,40 +3951,40 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403342</t>
+          <t xml:space="preserve">3204339</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J53">
-        <v>98</v>
+        <v>162</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199555</t>
+          <t xml:space="preserve">311477661</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t xml:space="preserve">JPH Energi A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2030-11-05</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4016,40 +4016,40 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagensvej 200A</t>
+          <t xml:space="preserve">Ved Skolen 2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">9028182</t>
+          <t xml:space="preserve">3177633</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J54">
-        <v>153</v>
+        <v>85</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466005</t>
+          <t xml:space="preserve">311485013</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-08</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4091,40 +4091,40 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsmarken 15B</t>
+          <t xml:space="preserve">Islandsgade 23</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">3204339</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J55">
-        <v>162</v>
+        <v>240</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477661</t>
+          <t xml:space="preserve">311485160</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-05</t>
+          <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4166,30 +4166,30 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Skolen 2</t>
+          <t xml:space="preserve">Enghavevej 2C</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177633</t>
+          <t xml:space="preserve">3150088</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J56">
-        <v>85</v>
+        <v>219</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485013</t>
+          <t xml:space="preserve">311494558</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4241,30 +4241,30 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Islandsgade 23</t>
+          <t xml:space="preserve">Skagensvej 131</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">5524072</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J57">
-        <v>240</v>
+        <v>87</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485160</t>
+          <t xml:space="preserve">311494570</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-28</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4316,30 +4316,30 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 2C</t>
+          <t xml:space="preserve">Spangkærvej 79</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">3150088</t>
+          <t xml:space="preserve">1403144</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J58">
-        <v>219</v>
+        <v>88</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494558</t>
+          <t xml:space="preserve">311494582</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagensvej 131</t>
+          <t xml:space="preserve">P Nørkjærs Plads 16</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4401,30 +4401,30 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524072</t>
+          <t xml:space="preserve">403893</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J59">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494570</t>
+          <t xml:space="preserve">311743993</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Domutech Solutions A/S</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2034-03-08</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4466,40 +4466,40 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spangkærvej 79</t>
+          <t xml:space="preserve">Højskolevej 11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403144</t>
+          <t xml:space="preserve">9796718</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J60">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494582</t>
+          <t xml:space="preserve">311879279</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Bygge-syn ApS</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4541,40 +4541,40 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">P Nørkjærs Plads 16</t>
+          <t xml:space="preserve">Jernbanegade 8C</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">403893</t>
+          <t xml:space="preserve">3213957</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J61">
-        <v>149</v>
+        <v>194</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743993</t>
+          <t xml:space="preserve">311885689</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech Solutions A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-08</t>
+          <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højskolevej 11</t>
+          <t xml:space="preserve">N C Jensensgade 2A</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">9796718</t>
+          <t xml:space="preserve">3177962</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4635,21 +4635,21 @@
         </is>
       </c>
       <c r="J62">
-        <v>103</v>
+        <v>222</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311879279</t>
+          <t xml:space="preserve">311886891</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygge-syn ApS</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-29</t>
+          <t xml:space="preserve">2036-03-11</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4691,30 +4691,30 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 8C</t>
+          <t xml:space="preserve">N C Jensensgade 2B</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">3213957</t>
+          <t xml:space="preserve">3177962</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J63">
-        <v>194</v>
+        <v>88</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885689</t>
+          <t xml:space="preserve">311886891</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-05</t>
+          <t xml:space="preserve">2036-03-11</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4766,30 +4766,30 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">N C Jensensgade 2A</t>
+          <t xml:space="preserve">Tannisbugtvej 24D</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177962</t>
+          <t xml:space="preserve">3155505</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J64">
-        <v>222</v>
+        <v>130</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886891</t>
+          <t xml:space="preserve">311887386</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-11</t>
+          <t xml:space="preserve">2036-03-13</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4841,30 +4841,30 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">N C Jensensgade 2B</t>
+          <t xml:space="preserve">Tannisbugtvej 24F</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177962</t>
+          <t xml:space="preserve">3155505</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J65">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886891</t>
+          <t xml:space="preserve">311887386</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-11</t>
+          <t xml:space="preserve">2036-03-13</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4916,30 +4916,30 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tannisbugtvej 24D</t>
+          <t xml:space="preserve">Færøvej 12</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">3155505</t>
+          <t xml:space="preserve">3170285</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J66">
-        <v>130</v>
+        <v>201</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887386</t>
+          <t xml:space="preserve">311890124</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-13</t>
+          <t xml:space="preserve">2036-03-25</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4991,30 +4991,30 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tannisbugtvej 24F</t>
+          <t xml:space="preserve">Færøvej 4</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">3155505</t>
+          <t xml:space="preserve">3170285</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J67">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887386</t>
+          <t xml:space="preserve">311890124</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-13</t>
+          <t xml:space="preserve">2036-03-25</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Færøvej 12</t>
+          <t xml:space="preserve">Færøvej 8</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5081,11 +5081,11 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J68">
-        <v>201</v>
+        <v>134</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5141,17 +5141,17 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Færøvej 4</t>
+          <t xml:space="preserve">Annasvej 14</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">3170285</t>
+          <t xml:space="preserve">5528700</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5160,11 +5160,11 @@
         </is>
       </c>
       <c r="J69">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311890124</t>
+          <t xml:space="preserve">311892239</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-25</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5216,17 +5216,17 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Færøvej 8</t>
+          <t xml:space="preserve">Sejlstrupvej 10</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">3170285</t>
+          <t xml:space="preserve">3161657</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5235,11 +5235,11 @@
         </is>
       </c>
       <c r="J70">
-        <v>134</v>
+        <v>184</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311890124</t>
+          <t xml:space="preserve">311893152</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-25</t>
+          <t xml:space="preserve">2036-04-09</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5291,30 +5291,30 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Annasvej 14</t>
+          <t xml:space="preserve">Studievej 7</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5528700</t>
+          <t xml:space="preserve">8540210</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J71">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892239</t>
+          <t xml:space="preserve">311894479</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-04-16</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5366,17 +5366,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sejlstrupvej 10</t>
+          <t xml:space="preserve">Skagensvej 200B</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">3161657</t>
+          <t xml:space="preserve">9028182</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5385,11 +5385,11 @@
         </is>
       </c>
       <c r="J72">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893152</t>
+          <t xml:space="preserve">311895956</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-09</t>
+          <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5441,30 +5441,30 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Studievej 7</t>
+          <t xml:space="preserve">Idræts Alle 45B</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">8540210</t>
+          <t xml:space="preserve">5522709</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J73">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894479</t>
+          <t xml:space="preserve">311912369</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-16</t>
+          <t xml:space="preserve">2036-07-02</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5516,30 +5516,30 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagensvej 200B</t>
+          <t xml:space="preserve">Vanggårdsgade 10B</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">9028182</t>
+          <t xml:space="preserve">7075274</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J74">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895956</t>
+          <t xml:space="preserve">311918201</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-22</t>
+          <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5606,15 +5606,15 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J75">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311912369</t>
+          <t xml:space="preserve">311921769</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-02</t>
+          <t xml:space="preserve">2036-08-26</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5666,30 +5666,30 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vanggårdsgade 10B</t>
+          <t xml:space="preserve">Frederikshavnsvej 70B</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">7075274</t>
+          <t xml:space="preserve">5526485</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J76">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918201</t>
+          <t xml:space="preserve">311922281</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-10</t>
+          <t xml:space="preserve">2036-08-28</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idræts Alle 45B</t>
+          <t xml:space="preserve">Elsagervej 25</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5751,20 +5751,20 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5522709</t>
+          <t xml:space="preserve">1808683</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J77">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311921769</t>
+          <t xml:space="preserve">311926230</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-26</t>
+          <t xml:space="preserve">2036-09-16</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederikshavnsvej 70B</t>
+          <t xml:space="preserve">Elsagervej 25A</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5826,20 +5826,20 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5526485</t>
+          <t xml:space="preserve">1808683</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J78">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922281</t>
+          <t xml:space="preserve">311926208</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-28</t>
+          <t xml:space="preserve">2036-09-16</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsagervej 25</t>
+          <t xml:space="preserve">Elsagervej 25B</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5906,15 +5906,15 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J79">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311926230</t>
+          <t xml:space="preserve">311926208</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsagervej 25A</t>
+          <t xml:space="preserve">Slettingenvej 51</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5976,20 +5976,20 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808683</t>
+          <t xml:space="preserve">1403342</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J80">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311926208</t>
+          <t xml:space="preserve">311931975</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-16</t>
+          <t xml:space="preserve">2036-10-15</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsagervej 25B</t>
+          <t xml:space="preserve">Slettingenvej 51</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6051,20 +6051,20 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808683</t>
+          <t xml:space="preserve">1403342</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J81">
-        <v>145</v>
+        <v>98</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311926208</t>
+          <t xml:space="preserve">311931976</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-16</t>
+          <t xml:space="preserve">2036-10-15</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
